--- a/TESE/EXTREMOS.xlsx
+++ b/TESE/EXTREMOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Documents\DOUTORADO\TESE\VICOSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Documents\Github\Lucasbpofc.github.io\TESE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3B2105-8CA8-4FAD-A749-A7BA13A09392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F977BD1-FFF2-43EA-8CDD-2BD31ADF093B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="705" windowWidth="20280" windowHeight="10155" activeTab="11" xr2:uid="{5F7D3377-E735-4169-8177-15EE5E51EA70}"/>
+    <workbookView xWindow="180" yWindow="1305" windowWidth="20175" windowHeight="8955" firstSheet="3" activeTab="11" xr2:uid="{5F7D3377-E735-4169-8177-15EE5E51EA70}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN" sheetId="1" r:id="rId1"/>
@@ -4642,10 +4642,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DEZ!$B$2:$B$66</c:f>
+              <c:f>DEZ!$B$2:$B$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>32.799999999999997</c:v>
                 </c:pt>
@@ -21659,15 +21659,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24757,7 +24757,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C11D9D-62C5-45EE-93B9-296139AFED8E}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -25552,11 +25552,6 @@
       </c>
       <c r="D56">
         <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="2">
-        <v>42369</v>
       </c>
     </row>
   </sheetData>

--- a/TESE/EXTREMOS.xlsx
+++ b/TESE/EXTREMOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Documents\Github\Lucasbpofc.github.io\TESE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F977BD1-FFF2-43EA-8CDD-2BD31ADF093B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F70EA9-17B6-47FE-8F8E-94A6CE2474EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="1305" windowWidth="20175" windowHeight="8955" firstSheet="3" activeTab="11" xr2:uid="{5F7D3377-E735-4169-8177-15EE5E51EA70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="11" xr2:uid="{5F7D3377-E735-4169-8177-15EE5E51EA70}"/>
   </bookViews>
   <sheets>
     <sheet name="JAN" sheetId="1" r:id="rId1"/>
@@ -4788,7 +4788,7 @@
                   <c:v>34.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>39.6</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>34.799999999999997</c:v>
@@ -25444,7 +25444,7 @@
         <v>2015</v>
       </c>
       <c r="B49" s="5">
-        <v>39.6</v>
+        <v>33</v>
       </c>
       <c r="C49" s="5">
         <v>69.8</v>
